--- a/output/pdf_financials_xlsx/RRR.UN.xlsx
+++ b/output/pdf_financials_xlsx/RRR.UN.xlsx
@@ -2142,37 +2142,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.407894</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.690932</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.248847</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.038419</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.117919</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.659808999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.251946</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>10.350519</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10.440231</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>14.481149</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>9.179817999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2232,37 +2232,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.407894</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.690932</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.248847</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.038419</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.117919</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>9.659808999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>9.251946</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>10.350519</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>10.440231</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>14.481149</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>9.179817999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2772,37 +2772,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.484544</v>
+        <v>0.07665</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.774908</v>
+        <v>0.083976</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.368735</v>
+        <v>0.119888</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.617412</v>
+        <v>0.578993</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.872587</v>
+        <v>0.754668</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>10.66316</v>
+        <v>1.003351</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>10.781081</v>
+        <v>1.529135</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>11.807203</v>
+        <v>1.456684</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>17.498792</v>
+        <v>7.058561</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>20.322085</v>
+        <v>5.840936</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>11.314654</v>
+        <v>2.134836</v>
       </c>
     </row>
     <row r="49">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -35542,7 +35542,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
